--- a/data/transactions/أذونات الإضافة لشهر 2.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8AEA0E-D5A6-4554-BD6A-EC3CA1A02F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D81EEA-0B5A-4A4F-A801-64E62023479D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -273,9 +271,6 @@
     <t>مفصله بلوم 90</t>
   </si>
   <si>
-    <t>ماران انا</t>
-  </si>
-  <si>
     <t>كود المورد</t>
   </si>
   <si>
@@ -1246,6 +1241,9 @@
   </si>
   <si>
     <t>بيان اذون الاضافة خلال الفترة من 2 فبراير الي 28 فبراير</t>
+  </si>
+  <si>
+    <t>ماران اثا</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1786,7 @@
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
       <c r="D3" s="18" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E3" s="18"/>
       <c r="F3" s="18"/>
@@ -1853,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>11</v>
@@ -1870,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>14</v>
@@ -1910,7 +1908,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>18</v>
@@ -1949,7 +1947,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>19</v>
@@ -1988,7 +1986,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>20</v>
@@ -2027,7 +2025,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -2066,7 +2064,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
@@ -2105,7 +2103,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>23</v>
@@ -2144,7 +2142,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>24</v>
@@ -2183,7 +2181,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>25</v>
@@ -2222,7 +2220,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>26</v>
@@ -2261,7 +2259,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>27</v>
@@ -2300,7 +2298,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>28</v>
@@ -2339,7 +2337,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>29</v>
@@ -2378,7 +2376,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>30</v>
@@ -2417,7 +2415,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>31</v>
@@ -2456,7 +2454,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
@@ -2495,7 +2493,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>33</v>
@@ -2534,7 +2532,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>34</v>
@@ -2573,10 +2571,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>15</v>
@@ -2612,7 +2610,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>35</v>
@@ -2651,7 +2649,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>36</v>
@@ -2690,7 +2688,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>37</v>
@@ -2729,7 +2727,7 @@
         <v>23</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>38</v>
@@ -2768,7 +2766,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>39</v>
@@ -2807,7 +2805,7 @@
         <v>25</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>40</v>
@@ -2846,7 +2844,7 @@
         <v>26</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>41</v>
@@ -2885,7 +2883,7 @@
         <v>27</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>42</v>
@@ -2924,7 +2922,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>43</v>
@@ -2963,7 +2961,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>44</v>
@@ -3002,7 +3000,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>45</v>
@@ -3041,7 +3039,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>46</v>
@@ -3080,7 +3078,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>47</v>
@@ -3119,7 +3117,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>48</v>
@@ -3158,7 +3156,7 @@
         <v>34</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>49</v>
@@ -3197,7 +3195,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>50</v>
@@ -3236,7 +3234,7 @@
         <v>36</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>51</v>
@@ -3275,7 +3273,7 @@
         <v>37</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>52</v>
@@ -3314,7 +3312,7 @@
         <v>38</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>53</v>
@@ -3353,7 +3351,7 @@
         <v>39</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>54</v>
@@ -3392,7 +3390,7 @@
         <v>40</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>55</v>
@@ -3431,7 +3429,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>56</v>
@@ -3470,10 +3468,10 @@
         <v>42</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>57</v>
@@ -3509,7 +3507,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>60</v>
@@ -3548,7 +3546,7 @@
         <v>44</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>62</v>
@@ -3587,7 +3585,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>63</v>
@@ -3626,7 +3624,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>66</v>
@@ -3665,7 +3663,7 @@
         <v>47</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>68</v>
@@ -3704,7 +3702,7 @@
         <v>48</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>70</v>
@@ -3743,7 +3741,7 @@
         <v>49</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>71</v>
@@ -3782,7 +3780,7 @@
         <v>50</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>73</v>
@@ -3821,7 +3819,7 @@
         <v>51</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>75</v>
@@ -3846,7 +3844,7 @@
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L57" s="4">
         <v>6162</v>
@@ -3860,10 +3858,10 @@
         <v>52</v>
       </c>
       <c r="B58" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>15</v>
@@ -3885,7 +3883,7 @@
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L58" s="4">
         <v>6162</v>
@@ -3899,10 +3897,10 @@
         <v>53</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>15</v>
@@ -3924,7 +3922,7 @@
       </c>
       <c r="J59" s="4"/>
       <c r="K59" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L59" s="4">
         <v>6162</v>
@@ -3938,10 +3936,10 @@
         <v>54</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>15</v>
@@ -3963,7 +3961,7 @@
       </c>
       <c r="J60" s="4"/>
       <c r="K60" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L60" s="4">
         <v>6162</v>
@@ -3977,10 +3975,10 @@
         <v>55</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>15</v>
@@ -4002,7 +4000,7 @@
       </c>
       <c r="J61" s="4"/>
       <c r="K61" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L61" s="4">
         <v>6162</v>
@@ -4016,10 +4014,10 @@
         <v>56</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>139</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>15</v>
@@ -4041,7 +4039,7 @@
       </c>
       <c r="J62" s="4"/>
       <c r="K62" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L62" s="4">
         <v>6162</v>
@@ -4055,10 +4053,10 @@
         <v>57</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>15</v>
@@ -4080,7 +4078,7 @@
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L63" s="4">
         <v>6162</v>
@@ -4094,10 +4092,10 @@
         <v>58</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>15</v>
@@ -4119,7 +4117,7 @@
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L64" s="4">
         <v>6162</v>
@@ -4133,10 +4131,10 @@
         <v>59</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>15</v>
@@ -4158,7 +4156,7 @@
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L65" s="4">
         <v>6162</v>
@@ -4172,10 +4170,10 @@
         <v>60</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>57</v>
@@ -4211,10 +4209,10 @@
         <v>61</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>15</v>
@@ -4236,7 +4234,7 @@
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L67" s="4">
         <v>6164</v>
@@ -4250,10 +4248,10 @@
         <v>62</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>15</v>
@@ -4275,7 +4273,7 @@
       </c>
       <c r="J68" s="4"/>
       <c r="K68" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L68" s="4">
         <v>6164</v>
@@ -4289,10 +4287,10 @@
         <v>63</v>
       </c>
       <c r="B69" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>15</v>
@@ -4314,7 +4312,7 @@
       </c>
       <c r="J69" s="4"/>
       <c r="K69" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L69" s="4">
         <v>6164</v>
@@ -4328,10 +4326,10 @@
         <v>64</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>15</v>
@@ -4353,7 +4351,7 @@
       </c>
       <c r="J70" s="4"/>
       <c r="K70" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L70" s="4">
         <v>6164</v>
@@ -4367,10 +4365,10 @@
         <v>65</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>15</v>
@@ -4392,7 +4390,7 @@
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L71" s="4">
         <v>6165</v>
@@ -4406,10 +4404,10 @@
         <v>66</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>15</v>
@@ -4431,7 +4429,7 @@
       </c>
       <c r="J72" s="4"/>
       <c r="K72" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L72" s="4">
         <v>6165</v>
@@ -4445,10 +4443,10 @@
         <v>67</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>15</v>
@@ -4470,7 +4468,7 @@
       </c>
       <c r="J73" s="4"/>
       <c r="K73" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L73" s="4">
         <v>6165</v>
@@ -4484,10 +4482,10 @@
         <v>68</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>15</v>
@@ -4509,7 +4507,7 @@
       </c>
       <c r="J74" s="4"/>
       <c r="K74" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L74" s="4">
         <v>6165</v>
@@ -4523,10 +4521,10 @@
         <v>69</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>15</v>
@@ -4548,7 +4546,7 @@
       </c>
       <c r="J75" s="4"/>
       <c r="K75" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L75" s="4">
         <v>6165</v>
@@ -4562,10 +4560,10 @@
         <v>70</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>15</v>
@@ -4587,7 +4585,7 @@
       </c>
       <c r="J76" s="4"/>
       <c r="K76" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L76" s="4">
         <v>6165</v>
@@ -4601,10 +4599,10 @@
         <v>71</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>15</v>
@@ -4626,7 +4624,7 @@
       </c>
       <c r="J77" s="4"/>
       <c r="K77" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L77" s="4">
         <v>6165</v>
@@ -4640,10 +4638,10 @@
         <v>72</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>15</v>
@@ -4665,7 +4663,7 @@
       </c>
       <c r="J78" s="4"/>
       <c r="K78" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L78" s="4">
         <v>6165</v>
@@ -4679,10 +4677,10 @@
         <v>73</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>15</v>
@@ -4704,7 +4702,7 @@
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L79" s="4">
         <v>6165</v>
@@ -4718,10 +4716,10 @@
         <v>74</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>15</v>
@@ -4743,7 +4741,7 @@
       </c>
       <c r="J80" s="4"/>
       <c r="K80" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L80" s="4">
         <v>6165</v>
@@ -4757,10 +4755,10 @@
         <v>75</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>15</v>
@@ -4782,7 +4780,7 @@
       </c>
       <c r="J81" s="4"/>
       <c r="K81" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L81" s="4">
         <v>6165</v>
@@ -4796,10 +4794,10 @@
         <v>76</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>15</v>
@@ -4821,7 +4819,7 @@
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L82" s="4">
         <v>6165</v>
@@ -4835,10 +4833,10 @@
         <v>77</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>15</v>
@@ -4860,7 +4858,7 @@
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L83" s="4">
         <v>6168</v>
@@ -4874,10 +4872,10 @@
         <v>78</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>15</v>
@@ -4899,7 +4897,7 @@
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L84" s="4">
         <v>6168</v>
@@ -4913,10 +4911,10 @@
         <v>79</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>15</v>
@@ -4938,7 +4936,7 @@
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L85" s="4">
         <v>6168</v>
@@ -4952,10 +4950,10 @@
         <v>80</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>15</v>
@@ -4977,7 +4975,7 @@
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L86" s="4">
         <v>6168</v>
@@ -4991,10 +4989,10 @@
         <v>81</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>15</v>
@@ -5016,7 +5014,7 @@
       </c>
       <c r="J87" s="4"/>
       <c r="K87" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L87" s="4">
         <v>6168</v>
@@ -5030,10 +5028,10 @@
         <v>82</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>15</v>
@@ -5055,7 +5053,7 @@
       </c>
       <c r="J88" s="4"/>
       <c r="K88" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L88" s="4">
         <v>6168</v>
@@ -5069,10 +5067,10 @@
         <v>83</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>15</v>
@@ -5094,7 +5092,7 @@
       </c>
       <c r="J89" s="4"/>
       <c r="K89" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L89" s="4">
         <v>6168</v>
@@ -5108,10 +5106,10 @@
         <v>84</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>15</v>
@@ -5129,11 +5127,11 @@
         <v>34343</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J90" s="4"/>
       <c r="K90" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L90" s="4">
         <v>6169</v>
@@ -5147,10 +5145,10 @@
         <v>85</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>15</v>
@@ -5168,11 +5166,11 @@
         <v>34343</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L91" s="4">
         <v>6169</v>
@@ -5186,10 +5184,10 @@
         <v>86</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>15</v>
@@ -5207,11 +5205,11 @@
         <v>34343</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L92" s="4">
         <v>6169</v>
@@ -5225,10 +5223,10 @@
         <v>87</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>15</v>
@@ -5246,11 +5244,11 @@
         <v>34343</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L93" s="4">
         <v>6169</v>
@@ -5264,10 +5262,10 @@
         <v>88</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>15</v>
@@ -5289,7 +5287,7 @@
       </c>
       <c r="J94" s="4"/>
       <c r="K94" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L94" s="4">
         <v>6167</v>
@@ -5303,10 +5301,10 @@
         <v>89</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>15</v>
@@ -5328,7 +5326,7 @@
       </c>
       <c r="J95" s="4"/>
       <c r="K95" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L95" s="4">
         <v>6167</v>
@@ -5342,10 +5340,10 @@
         <v>90</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>15</v>
@@ -5367,7 +5365,7 @@
       </c>
       <c r="J96" s="4"/>
       <c r="K96" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L96" s="4">
         <v>6167</v>
@@ -5381,10 +5379,10 @@
         <v>91</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>15</v>
@@ -5406,7 +5404,7 @@
       </c>
       <c r="J97" s="4"/>
       <c r="K97" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L97" s="4">
         <v>6170</v>
@@ -5420,10 +5418,10 @@
         <v>92</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>57</v>
@@ -5445,7 +5443,7 @@
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L98" s="4">
         <v>6170</v>
@@ -5459,10 +5457,10 @@
         <v>93</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>15</v>
@@ -5480,11 +5478,11 @@
         <v>4368</v>
       </c>
       <c r="I99" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J99" s="4"/>
       <c r="K99" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L99" s="4">
         <v>6171</v>
@@ -5498,10 +5496,10 @@
         <v>94</v>
       </c>
       <c r="B100" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>15</v>
@@ -5519,11 +5517,11 @@
         <v>4368</v>
       </c>
       <c r="I100" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J100" s="4"/>
       <c r="K100" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L100" s="4">
         <v>6171</v>
@@ -5537,10 +5535,10 @@
         <v>95</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>15</v>
@@ -5558,11 +5556,11 @@
         <v>4368</v>
       </c>
       <c r="I101" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J101" s="4"/>
       <c r="K101" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L101" s="4">
         <v>6171</v>
@@ -5576,10 +5574,10 @@
         <v>96</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>15</v>
@@ -5597,11 +5595,11 @@
         <v>4368</v>
       </c>
       <c r="I102" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L102" s="4">
         <v>6171</v>
@@ -5615,10 +5613,10 @@
         <v>97</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>15</v>
@@ -5636,11 +5634,11 @@
         <v>4368</v>
       </c>
       <c r="I103" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J103" s="4"/>
       <c r="K103" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L103" s="4">
         <v>6171</v>
@@ -5654,10 +5652,10 @@
         <v>98</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>15</v>
@@ -5675,11 +5673,11 @@
         <v>20</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L104" s="4">
         <v>6172</v>
@@ -5693,10 +5691,10 @@
         <v>99</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>15</v>
@@ -5714,11 +5712,11 @@
         <v>20</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L105" s="4">
         <v>6172</v>
@@ -5732,10 +5730,10 @@
         <v>100</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>15</v>
@@ -5753,11 +5751,11 @@
         <v>20</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J106" s="4"/>
       <c r="K106" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L106" s="4">
         <v>6172</v>
@@ -5771,10 +5769,10 @@
         <v>101</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>15</v>
@@ -5792,11 +5790,11 @@
         <v>20</v>
       </c>
       <c r="I107" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J107" s="4"/>
       <c r="K107" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L107" s="4">
         <v>6172</v>
@@ -5810,10 +5808,10 @@
         <v>102</v>
       </c>
       <c r="B108" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>15</v>
@@ -5831,11 +5829,11 @@
         <v>20</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J108" s="4"/>
       <c r="K108" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L108" s="4">
         <v>6172</v>
@@ -5849,10 +5847,10 @@
         <v>103</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>15</v>
@@ -5870,11 +5868,11 @@
         <v>20</v>
       </c>
       <c r="I109" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J109" s="4"/>
       <c r="K109" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L109" s="4">
         <v>6172</v>
@@ -5888,10 +5886,10 @@
         <v>104</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>15</v>
@@ -5909,11 +5907,11 @@
         <v>20</v>
       </c>
       <c r="I110" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L110" s="4">
         <v>6172</v>
@@ -5927,10 +5925,10 @@
         <v>105</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>15</v>
@@ -5948,11 +5946,11 @@
         <v>20</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L111" s="4">
         <v>6172</v>
@@ -5966,10 +5964,10 @@
         <v>106</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>15</v>
@@ -5987,11 +5985,11 @@
         <v>20</v>
       </c>
       <c r="I112" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L112" s="4">
         <v>6172</v>
@@ -6005,10 +6003,10 @@
         <v>107</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>15</v>
@@ -6026,11 +6024,11 @@
         <v>20</v>
       </c>
       <c r="I113" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L113" s="4">
         <v>6172</v>
@@ -6044,10 +6042,10 @@
         <v>108</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>15</v>
@@ -6065,11 +6063,11 @@
         <v>20</v>
       </c>
       <c r="I114" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J114" s="4"/>
       <c r="K114" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L114" s="4">
         <v>6172</v>
@@ -6083,10 +6081,10 @@
         <v>109</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>15</v>
@@ -6104,7 +6102,7 @@
         <v>5102</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="3" t="s">
@@ -6122,10 +6120,10 @@
         <v>110</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>15</v>
@@ -6143,7 +6141,7 @@
         <v>2433</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="3" t="s">
@@ -6161,10 +6159,10 @@
         <v>111</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>15</v>
@@ -6182,7 +6180,7 @@
         <v>2433</v>
       </c>
       <c r="I117" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J117" s="4"/>
       <c r="K117" s="3" t="s">
@@ -6200,10 +6198,10 @@
         <v>112</v>
       </c>
       <c r="B118" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>15</v>
@@ -6221,7 +6219,7 @@
         <v>2433</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J118" s="4"/>
       <c r="K118" s="3" t="s">
@@ -6239,10 +6237,10 @@
         <v>113</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>15</v>
@@ -6260,7 +6258,7 @@
         <v>2433</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J119" s="4"/>
       <c r="K119" s="3" t="s">
@@ -6278,10 +6276,10 @@
         <v>114</v>
       </c>
       <c r="B120" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>15</v>
@@ -6299,7 +6297,7 @@
         <v>2433</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J120" s="4"/>
       <c r="K120" s="3" t="s">
@@ -6317,10 +6315,10 @@
         <v>115</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>15</v>
@@ -6338,7 +6336,7 @@
         <v>2433</v>
       </c>
       <c r="I121" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J121" s="4"/>
       <c r="K121" s="3" t="s">
@@ -6356,10 +6354,10 @@
         <v>116</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>15</v>
@@ -6377,7 +6375,7 @@
         <v>2433</v>
       </c>
       <c r="I122" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J122" s="4"/>
       <c r="K122" s="3" t="s">
@@ -6395,10 +6393,10 @@
         <v>117</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>15</v>
@@ -6416,7 +6414,7 @@
         <v>2433</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J123" s="4"/>
       <c r="K123" s="3" t="s">
@@ -6434,10 +6432,10 @@
         <v>118</v>
       </c>
       <c r="B124" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>15</v>
@@ -6455,7 +6453,7 @@
         <v>2433</v>
       </c>
       <c r="I124" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J124" s="4"/>
       <c r="K124" s="3" t="s">
@@ -6473,10 +6471,10 @@
         <v>119</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>15</v>
@@ -6494,7 +6492,7 @@
         <v>2433</v>
       </c>
       <c r="I125" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J125" s="4"/>
       <c r="K125" s="3" t="s">
@@ -6512,10 +6510,10 @@
         <v>120</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>15</v>
@@ -6533,7 +6531,7 @@
         <v>2433</v>
       </c>
       <c r="I126" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J126" s="4"/>
       <c r="K126" s="3" t="s">
@@ -6551,10 +6549,10 @@
         <v>121</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>15</v>
@@ -6572,7 +6570,7 @@
         <v>2433</v>
       </c>
       <c r="I127" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J127" s="4"/>
       <c r="K127" s="3" t="s">
@@ -6590,10 +6588,10 @@
         <v>122</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>15</v>
@@ -6611,7 +6609,7 @@
         <v>2433</v>
       </c>
       <c r="I128" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J128" s="4"/>
       <c r="K128" s="3" t="s">
@@ -6629,10 +6627,10 @@
         <v>123</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>15</v>
@@ -6650,7 +6648,7 @@
         <v>2433</v>
       </c>
       <c r="I129" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J129" s="4"/>
       <c r="K129" s="3" t="s">
@@ -6668,13 +6666,13 @@
         <v>124</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C130" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D130" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="D130" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="E130" s="4">
         <v>12</v>
@@ -6689,7 +6687,7 @@
         <v>5099</v>
       </c>
       <c r="I130" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J130" s="4"/>
       <c r="K130" s="3" t="s">
@@ -6707,10 +6705,10 @@
         <v>125</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>57</v>
@@ -6728,11 +6726,11 @@
         <v>695</v>
       </c>
       <c r="I131" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J131" s="4"/>
       <c r="K131" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L131" s="4">
         <v>6177</v>
@@ -6746,10 +6744,10 @@
         <v>126</v>
       </c>
       <c r="B132" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>15</v>
@@ -6767,7 +6765,7 @@
         <v>13650</v>
       </c>
       <c r="I132" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J132" s="4"/>
       <c r="K132" s="3" t="s">
@@ -6785,10 +6783,10 @@
         <v>127</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>15</v>
@@ -6806,7 +6804,7 @@
         <v>13650</v>
       </c>
       <c r="I133" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J133" s="4"/>
       <c r="K133" s="3" t="s">
@@ -6824,10 +6822,10 @@
         <v>128</v>
       </c>
       <c r="B134" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>15</v>
@@ -6845,7 +6843,7 @@
         <v>13650</v>
       </c>
       <c r="I134" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J134" s="4"/>
       <c r="K134" s="3" t="s">
@@ -6863,10 +6861,10 @@
         <v>129</v>
       </c>
       <c r="B135" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>15</v>
@@ -6884,7 +6882,7 @@
         <v>13650</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J135" s="4"/>
       <c r="K135" s="3" t="s">
@@ -6902,10 +6900,10 @@
         <v>130</v>
       </c>
       <c r="B136" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>15</v>
@@ -6923,7 +6921,7 @@
         <v>13650</v>
       </c>
       <c r="I136" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J136" s="4"/>
       <c r="K136" s="3" t="s">
@@ -6941,10 +6939,10 @@
         <v>131</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>15</v>
@@ -6962,11 +6960,11 @@
         <v>11720</v>
       </c>
       <c r="I137" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J137" s="4"/>
       <c r="K137" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L137" s="4">
         <v>6179</v>
@@ -6980,10 +6978,10 @@
         <v>132</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>15</v>
@@ -7001,11 +6999,11 @@
         <v>11720</v>
       </c>
       <c r="I138" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J138" s="4"/>
       <c r="K138" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L138" s="4">
         <v>6179</v>
@@ -7019,10 +7017,10 @@
         <v>133</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>15</v>
@@ -7040,11 +7038,11 @@
         <v>11720</v>
       </c>
       <c r="I139" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J139" s="4"/>
       <c r="K139" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L139" s="4">
         <v>6179</v>
@@ -7058,10 +7056,10 @@
         <v>134</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>15</v>
@@ -7079,11 +7077,11 @@
         <v>11720</v>
       </c>
       <c r="I140" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J140" s="4"/>
       <c r="K140" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L140" s="4">
         <v>6179</v>
@@ -7097,10 +7095,10 @@
         <v>135</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>15</v>
@@ -7118,11 +7116,11 @@
         <v>11720</v>
       </c>
       <c r="I141" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J141" s="4"/>
       <c r="K141" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L141" s="4">
         <v>6179</v>
@@ -7136,10 +7134,10 @@
         <v>136</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>15</v>
@@ -7157,11 +7155,11 @@
         <v>11720</v>
       </c>
       <c r="I142" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J142" s="4"/>
       <c r="K142" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L142" s="4">
         <v>6179</v>
@@ -7175,10 +7173,10 @@
         <v>137</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>15</v>
@@ -7196,11 +7194,11 @@
         <v>11720</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J143" s="4"/>
       <c r="K143" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L143" s="4">
         <v>6179</v>
@@ -7214,10 +7212,10 @@
         <v>138</v>
       </c>
       <c r="B144" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="C144" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>15</v>
@@ -7235,11 +7233,11 @@
         <v>11720</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J144" s="4"/>
       <c r="K144" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L144" s="4">
         <v>6179</v>
@@ -7253,10 +7251,10 @@
         <v>139</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>57</v>
@@ -7274,11 +7272,11 @@
         <v>1641</v>
       </c>
       <c r="I145" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J145" s="4"/>
       <c r="K145" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L145" s="4">
         <v>6180</v>
@@ -7292,10 +7290,10 @@
         <v>140</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>57</v>
@@ -7313,11 +7311,11 @@
         <v>59725</v>
       </c>
       <c r="I146" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J146" s="4"/>
       <c r="K146" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L146" s="4">
         <v>6181</v>
@@ -7331,10 +7329,10 @@
         <v>141</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>57</v>
@@ -7352,11 +7350,11 @@
         <v>59725</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J147" s="4"/>
       <c r="K147" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L147" s="4">
         <v>6181</v>
@@ -7370,10 +7368,10 @@
         <v>142</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>15</v>
@@ -7391,11 +7389,11 @@
         <v>324065</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J148" s="4"/>
       <c r="K148" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L148" s="4">
         <v>6182</v>
@@ -7409,10 +7407,10 @@
         <v>143</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>15</v>
@@ -7424,17 +7422,17 @@
         <v>767</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H149" s="14">
         <v>324065</v>
       </c>
       <c r="I149" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J149" s="4"/>
       <c r="K149" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L149" s="4">
         <v>6182</v>
@@ -7448,10 +7446,10 @@
         <v>144</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>15</v>
@@ -7469,11 +7467,11 @@
         <v>324065</v>
       </c>
       <c r="I150" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J150" s="4"/>
       <c r="K150" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L150" s="4">
         <v>6182</v>
@@ -7487,10 +7485,10 @@
         <v>145</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>15</v>
@@ -7508,11 +7506,11 @@
         <v>324065</v>
       </c>
       <c r="I151" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J151" s="4"/>
       <c r="K151" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L151" s="4">
         <v>6182</v>
@@ -7526,10 +7524,10 @@
         <v>146</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>15</v>
@@ -7547,11 +7545,11 @@
         <v>324065</v>
       </c>
       <c r="I152" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J152" s="4"/>
       <c r="K152" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L152" s="4">
         <v>6182</v>
@@ -7565,10 +7563,10 @@
         <v>147</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>15</v>
@@ -7586,11 +7584,11 @@
         <v>324065</v>
       </c>
       <c r="I153" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J153" s="4"/>
       <c r="K153" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L153" s="4">
         <v>6182</v>
@@ -7604,10 +7602,10 @@
         <v>148</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>15</v>
@@ -7625,11 +7623,11 @@
         <v>324065</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J154" s="4"/>
       <c r="K154" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L154" s="4">
         <v>6182</v>
@@ -7643,10 +7641,10 @@
         <v>149</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>15</v>
@@ -7664,11 +7662,11 @@
         <v>324065</v>
       </c>
       <c r="I155" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J155" s="4"/>
       <c r="K155" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L155" s="4">
         <v>6182</v>
@@ -7682,10 +7680,10 @@
         <v>150</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>15</v>
@@ -7703,11 +7701,11 @@
         <v>324065</v>
       </c>
       <c r="I156" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J156" s="4"/>
       <c r="K156" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L156" s="4">
         <v>6182</v>
@@ -7721,10 +7719,10 @@
         <v>151</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>15</v>
@@ -7742,11 +7740,11 @@
         <v>324065</v>
       </c>
       <c r="I157" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="J157" s="4"/>
       <c r="K157" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L157" s="4">
         <v>6182</v>
@@ -7760,10 +7758,10 @@
         <v>152</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>15</v>
@@ -7781,17 +7779,17 @@
         <v>694</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J158" s="4"/>
       <c r="K158" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L158" s="4">
         <v>6183</v>
       </c>
       <c r="M158" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7799,10 +7797,10 @@
         <v>153</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>15</v>
@@ -7820,17 +7818,17 @@
         <v>694</v>
       </c>
       <c r="I159" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J159" s="4"/>
       <c r="K159" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L159" s="4">
         <v>6183</v>
       </c>
       <c r="M159" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7838,10 +7836,10 @@
         <v>154</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>15</v>
@@ -7859,17 +7857,17 @@
         <v>694</v>
       </c>
       <c r="I160" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J160" s="4"/>
       <c r="K160" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L160" s="4">
         <v>6183</v>
       </c>
       <c r="M160" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7877,10 +7875,10 @@
         <v>155</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>15</v>
@@ -7898,17 +7896,17 @@
         <v>694</v>
       </c>
       <c r="I161" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J161" s="4"/>
       <c r="K161" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L161" s="4">
         <v>6183</v>
       </c>
       <c r="M161" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7916,10 +7914,10 @@
         <v>156</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>15</v>
@@ -7937,17 +7935,17 @@
         <v>694</v>
       </c>
       <c r="I162" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J162" s="4"/>
       <c r="K162" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L162" s="4">
         <v>6183</v>
       </c>
       <c r="M162" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7955,10 +7953,10 @@
         <v>157</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>15</v>
@@ -7976,17 +7974,17 @@
         <v>694</v>
       </c>
       <c r="I163" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J163" s="4"/>
       <c r="K163" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L163" s="4">
         <v>6183</v>
       </c>
       <c r="M163" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -7994,10 +7992,10 @@
         <v>158</v>
       </c>
       <c r="B164" s="12" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>15</v>
@@ -8019,13 +8017,13 @@
       </c>
       <c r="J164" s="4"/>
       <c r="K164" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L164" s="4">
         <v>6184</v>
       </c>
       <c r="M164" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8033,10 +8031,10 @@
         <v>159</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>15</v>
@@ -8058,13 +8056,13 @@
       </c>
       <c r="J165" s="4"/>
       <c r="K165" s="3" t="s">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="L165" s="4">
         <v>6184</v>
       </c>
       <c r="M165" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8072,10 +8070,10 @@
         <v>160</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>57</v>
@@ -8097,13 +8095,13 @@
       </c>
       <c r="J166" s="4"/>
       <c r="K166" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L166" s="4">
         <v>6185</v>
       </c>
       <c r="M166" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8111,10 +8109,10 @@
         <v>161</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>15</v>
@@ -8136,13 +8134,13 @@
       </c>
       <c r="J167" s="4"/>
       <c r="K167" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L167" s="4">
         <v>6185</v>
       </c>
       <c r="M167" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8150,10 +8148,10 @@
         <v>162</v>
       </c>
       <c r="B168" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>57</v>
@@ -8175,13 +8173,13 @@
       </c>
       <c r="J168" s="4"/>
       <c r="K168" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L168" s="4">
         <v>6185</v>
       </c>
       <c r="M168" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8189,10 +8187,10 @@
         <v>163</v>
       </c>
       <c r="B169" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="C169" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>15</v>
@@ -8220,7 +8218,7 @@
         <v>6186</v>
       </c>
       <c r="M169" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8228,13 +8226,13 @@
         <v>164</v>
       </c>
       <c r="B170" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E170" s="4">
         <v>8</v>
@@ -8249,17 +8247,17 @@
         <v>4369</v>
       </c>
       <c r="I170" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J170" s="4"/>
       <c r="K170" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L170" s="4">
         <v>6187</v>
       </c>
       <c r="M170" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8267,10 +8265,10 @@
         <v>165</v>
       </c>
       <c r="B171" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>15</v>
@@ -8288,17 +8286,17 @@
         <v>4369</v>
       </c>
       <c r="I171" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J171" s="4"/>
       <c r="K171" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L171" s="4">
         <v>6187</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8306,10 +8304,10 @@
         <v>166</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>15</v>
@@ -8327,17 +8325,17 @@
         <v>4369</v>
       </c>
       <c r="I172" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J172" s="4"/>
       <c r="K172" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L172" s="4">
         <v>6187</v>
       </c>
       <c r="M172" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8345,10 +8343,10 @@
         <v>167</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>15</v>
@@ -8366,17 +8364,17 @@
         <v>4369</v>
       </c>
       <c r="I173" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J173" s="4"/>
       <c r="K173" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L173" s="4">
         <v>6187</v>
       </c>
       <c r="M173" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8384,10 +8382,10 @@
         <v>168</v>
       </c>
       <c r="B174" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>15</v>
@@ -8405,17 +8403,17 @@
         <v>4369</v>
       </c>
       <c r="I174" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J174" s="4"/>
       <c r="K174" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L174" s="4">
         <v>6187</v>
       </c>
       <c r="M174" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8423,10 +8421,10 @@
         <v>169</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>15</v>
@@ -8444,17 +8442,17 @@
         <v>4369</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J175" s="4"/>
       <c r="K175" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L175" s="4">
         <v>6187</v>
       </c>
       <c r="M175" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8462,10 +8460,10 @@
         <v>170</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>15</v>
@@ -8483,17 +8481,17 @@
         <v>4369</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J176" s="4"/>
       <c r="K176" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L176" s="4">
         <v>6187</v>
       </c>
       <c r="M176" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8501,10 +8499,10 @@
         <v>171</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>15</v>
@@ -8522,17 +8520,17 @@
         <v>4369</v>
       </c>
       <c r="I177" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J177" s="4"/>
       <c r="K177" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L177" s="4">
         <v>6187</v>
       </c>
       <c r="M177" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8540,10 +8538,10 @@
         <v>172</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>15</v>
@@ -8561,17 +8559,17 @@
         <v>4369</v>
       </c>
       <c r="I178" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J178" s="4"/>
       <c r="K178" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L178" s="4">
         <v>6187</v>
       </c>
       <c r="M178" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8579,10 +8577,10 @@
         <v>173</v>
       </c>
       <c r="B179" s="12" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>15</v>
@@ -8600,17 +8598,17 @@
         <v>4369</v>
       </c>
       <c r="I179" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J179" s="4"/>
       <c r="K179" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L179" s="4">
         <v>6187</v>
       </c>
       <c r="M179" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8618,10 +8616,10 @@
         <v>174</v>
       </c>
       <c r="B180" s="12" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>15</v>
@@ -8639,17 +8637,17 @@
         <v>4369</v>
       </c>
       <c r="I180" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J180" s="4"/>
       <c r="K180" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L180" s="4">
         <v>6187</v>
       </c>
       <c r="M180" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8657,10 +8655,10 @@
         <v>175</v>
       </c>
       <c r="B181" s="12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>15</v>
@@ -8678,17 +8676,17 @@
         <v>4369</v>
       </c>
       <c r="I181" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J181" s="4"/>
       <c r="K181" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L181" s="4">
         <v>6187</v>
       </c>
       <c r="M181" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8696,10 +8694,10 @@
         <v>176</v>
       </c>
       <c r="B182" s="12" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>15</v>
@@ -8717,17 +8715,17 @@
         <v>4369</v>
       </c>
       <c r="I182" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J182" s="4"/>
       <c r="K182" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L182" s="4">
         <v>6188</v>
       </c>
       <c r="M182" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8735,10 +8733,10 @@
         <v>177</v>
       </c>
       <c r="B183" s="12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>15</v>
@@ -8756,17 +8754,17 @@
         <v>4369</v>
       </c>
       <c r="I183" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J183" s="4"/>
       <c r="K183" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L183" s="4">
         <v>6188</v>
       </c>
       <c r="M183" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8774,10 +8772,10 @@
         <v>178</v>
       </c>
       <c r="B184" s="12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>15</v>
@@ -8795,17 +8793,17 @@
         <v>4369</v>
       </c>
       <c r="I184" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J184" s="4"/>
       <c r="K184" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L184" s="4">
         <v>6188</v>
       </c>
       <c r="M184" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8813,10 +8811,10 @@
         <v>179</v>
       </c>
       <c r="B185" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>15</v>
@@ -8834,17 +8832,17 @@
         <v>4369</v>
       </c>
       <c r="I185" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J185" s="4"/>
       <c r="K185" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L185" s="4">
         <v>6188</v>
       </c>
       <c r="M185" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8852,10 +8850,10 @@
         <v>180</v>
       </c>
       <c r="B186" s="12" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>15</v>
@@ -8873,17 +8871,17 @@
         <v>4369</v>
       </c>
       <c r="I186" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J186" s="4"/>
       <c r="K186" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L186" s="4">
         <v>6188</v>
       </c>
       <c r="M186" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8950,6 +8948,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="69" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="69" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/transactions/أذونات الإضافة لشهر 2.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D81EEA-0B5A-4A4F-A801-64E62023479D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDE419E-E2E8-46AB-99E0-BCECD3363191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1758,7 +1758,7 @@
     <col min="3" max="3" width="31.28515625" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="10" width="18.7109375" customWidth="1"/>
@@ -4176,13 +4176,13 @@
         <v>160</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="E66" s="4">
-        <v>2850</v>
+        <v>2</v>
       </c>
       <c r="F66" s="4">
-        <v>40</v>
+        <v>57000</v>
       </c>
       <c r="G66" s="4">
         <v>114000</v>
